--- a/docs/Chicago-Toastmasters-Clubs.xlsx
+++ b/docs/Chicago-Toastmasters-Clubs.xlsx
@@ -3934,7 +3934,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Lombard, Il, IL</t>
+          <t>Lombard, IL</t>
         </is>
       </c>
       <c r="G42" s="11" t="inlineStr">
